--- a/synergy_raw.xlsx
+++ b/synergy_raw.xlsx
@@ -40,33 +40,33 @@
     <font>
       <name val="Arial"/>
       <color rgb="00374151"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="001155CC"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,11 +81,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="003D6BB5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F5FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -142,13 +137,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -581,12 +573,12 @@
           <t>delivery_results</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_results</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>配信結果取得API（CSV）。1配信成功宛先1行。</t>
         </is>
@@ -615,12 +607,12 @@
           <t>delivery_clicks</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_clicks</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>クリックフィードバック結果取得API（CSV）。1クリックイベント1行。</t>
         </is>
@@ -649,12 +641,12 @@
           <t>delivery_unsubscribes</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_unsubscribes</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>配信解除依頼リスト取得API（CSV）。1解除依頼1行。</t>
         </is>
@@ -696,44 +688,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>raw_synergy_deliveries</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>API名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>BQ名</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>BQ型</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -777,37 +769,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>配信状態（SENDING / COMPLETED / RESERVED / ERROR）</t>
         </is>
@@ -851,37 +843,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>sent</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>sent</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>INT64</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>配信完了数</t>
         </is>
@@ -925,37 +917,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>配信設定時 fromName</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>from_name</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>NULLABLE</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>差出人名</t>
         </is>
@@ -999,37 +991,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>配信設定時 subject</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>subject</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>メール件名</t>
         </is>
@@ -1073,37 +1065,37 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>配信設定時 test</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>テスト配信フラグ</t>
         </is>
@@ -1173,44 +1165,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_results</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>CSV列名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>BQ名</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>BQ型</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1254,37 +1246,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Synergy!ID</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>synergy_id</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>INT64</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Synergy! 顧客ID（配信時に付与した Customer.synergyid）</t>
         </is>
@@ -1328,37 +1320,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>取込時付与</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>loaded_date</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>取込日（パーティションキー）</t>
         </is>
@@ -1391,44 +1383,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_opens</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>CSV列名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>BQ名</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>BQ型</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1472,37 +1464,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Synergy!ID</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>synergy_id</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>INT64</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Synergy! 顧客ID</t>
         </is>
@@ -1546,37 +1538,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>取込時付与</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>loaded_date</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>取込日（パーティションキー）</t>
         </is>
@@ -1609,44 +1601,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_clicks</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>CSV列名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>BQ名</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>BQ型</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1690,37 +1682,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Synergy!ID</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>synergy_id</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>INT64</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Synergy! 顧客ID</t>
         </is>
@@ -1764,37 +1756,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>クリックID</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>click_feedback_id</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>INT64</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>クリックフィードバックID（配信レスポンスのtextClickFeedbacks/htmlClickFeedbacksのidに対応）</t>
         </is>
@@ -1838,37 +1830,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>取込時付与</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>loaded_date</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>取込日（パーティションキー）</t>
         </is>
@@ -1901,44 +1893,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_errors</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>CSV列名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>BQ名</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>BQ型</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1982,37 +1974,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Synergy!ID</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>synergy_id</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>INT64</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Synergy! 顧客ID</t>
         </is>
@@ -2056,37 +2048,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>配信エラー理由</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>error_reason</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>STRING</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>エラーコード（下記参照）</t>
         </is>
@@ -2156,44 +2148,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>raw_synergy_delivery_unsubscribes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>CSV列名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>BQ名</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>BQ型</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>モード</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -2237,37 +2229,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Synergy!ID</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>synergy_id</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>INT64</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Synergy! 顧客ID</t>
         </is>
@@ -2311,37 +2303,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>取込時付与</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>loaded_date</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>REQUIRED</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>取込日（パーティションキー）</t>
         </is>
